--- a/resources/templates/Report on Appointment Issued.xlsx
+++ b/resources/templates/Report on Appointment Issued.xlsx
@@ -179,7 +179,7 @@
     <t>${position}</t>
   </si>
   <si>
-    <t>OSEC-DECSB-TCH1-270941-2026</t>
+    <t>${plantilla_number}</t>
   </si>
   <si>
     <t>${salary_grade}</t>

--- a/resources/templates/Report on Appointment Issued.xlsx
+++ b/resources/templates/Report on Appointment Issued.xlsx
@@ -161,7 +161,7 @@
     <t>Date of Release (mm/dd/yyyy)</t>
   </si>
   <si>
-    <t>06/22/2026</t>
+    <t>${date_of_signing}</t>
   </si>
   <si>
     <t>${last_name}</t>
@@ -813,16 +813,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1861,7 +1861,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2062,7 +2062,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="27" fillId="0" borderId="38" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="38" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2090,6 +2090,10 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="27" fillId="0" borderId="38" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2159,9 +2163,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="58" fontId="27" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -3197,7 +3198,7 @@
       <c r="A25" s="90">
         <v>1</v>
       </c>
-      <c r="B25" s="135" t="s">
+      <c r="B25" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C25" s="92" t="s">
@@ -3262,13 +3263,13 @@
       <c r="F26" s="102"/>
       <c r="G26" s="93"/>
       <c r="H26" s="103"/>
-      <c r="I26" s="95"/>
+      <c r="I26" s="104"/>
       <c r="J26" s="96"/>
-      <c r="K26" s="104"/>
-      <c r="L26" s="104"/>
-      <c r="M26" s="104"/>
-      <c r="N26" s="104"/>
-      <c r="O26" s="104"/>
+      <c r="K26" s="105"/>
+      <c r="L26" s="105"/>
+      <c r="M26" s="105"/>
+      <c r="N26" s="105"/>
+      <c r="O26" s="105"/>
       <c r="P26" s="97"/>
       <c r="Q26" s="97"/>
       <c r="R26" s="98"/>
@@ -3286,19 +3287,19 @@
         <v>3</v>
       </c>
       <c r="B27" s="101"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="105"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="106"/>
       <c r="E27" s="102"/>
       <c r="F27" s="102"/>
       <c r="G27" s="93"/>
       <c r="H27" s="103"/>
-      <c r="I27" s="95"/>
+      <c r="I27" s="104"/>
       <c r="J27" s="96"/>
-      <c r="K27" s="104"/>
-      <c r="L27" s="104"/>
-      <c r="M27" s="104"/>
-      <c r="N27" s="104"/>
-      <c r="O27" s="104"/>
+      <c r="K27" s="105"/>
+      <c r="L27" s="105"/>
+      <c r="M27" s="105"/>
+      <c r="N27" s="105"/>
+      <c r="O27" s="105"/>
       <c r="P27" s="97"/>
       <c r="Q27" s="97"/>
       <c r="R27" s="98"/>
@@ -3316,19 +3317,19 @@
         <v>4</v>
       </c>
       <c r="B28" s="101"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="106"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="107"/>
       <c r="E28" s="102"/>
-      <c r="F28" s="106"/>
+      <c r="F28" s="107"/>
       <c r="G28" s="93"/>
       <c r="H28" s="103"/>
-      <c r="I28" s="95"/>
+      <c r="I28" s="104"/>
       <c r="J28" s="96"/>
-      <c r="K28" s="104"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="104"/>
-      <c r="N28" s="104"/>
-      <c r="O28" s="104"/>
+      <c r="K28" s="105"/>
+      <c r="L28" s="105"/>
+      <c r="M28" s="105"/>
+      <c r="N28" s="105"/>
+      <c r="O28" s="105"/>
       <c r="P28" s="97"/>
       <c r="Q28" s="97"/>
       <c r="R28" s="98"/>
@@ -3346,19 +3347,19 @@
         <v>5</v>
       </c>
       <c r="B29" s="101"/>
-      <c r="C29" s="106"/>
-      <c r="D29" s="106"/>
+      <c r="C29" s="107"/>
+      <c r="D29" s="107"/>
       <c r="E29" s="102"/>
-      <c r="F29" s="106"/>
+      <c r="F29" s="107"/>
       <c r="G29" s="93"/>
       <c r="H29" s="103"/>
-      <c r="I29" s="95"/>
+      <c r="I29" s="104"/>
       <c r="J29" s="96"/>
-      <c r="K29" s="104"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="104"/>
-      <c r="N29" s="104"/>
-      <c r="O29" s="104"/>
+      <c r="K29" s="105"/>
+      <c r="L29" s="105"/>
+      <c r="M29" s="105"/>
+      <c r="N29" s="105"/>
+      <c r="O29" s="105"/>
       <c r="P29" s="97"/>
       <c r="Q29" s="97"/>
       <c r="R29" s="98"/>
@@ -3376,19 +3377,19 @@
         <v>6</v>
       </c>
       <c r="B30" s="101"/>
-      <c r="C30" s="106"/>
-      <c r="D30" s="106"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="107"/>
       <c r="E30" s="102"/>
-      <c r="F30" s="106"/>
+      <c r="F30" s="107"/>
       <c r="G30" s="93"/>
       <c r="H30" s="103"/>
-      <c r="I30" s="95"/>
+      <c r="I30" s="104"/>
       <c r="J30" s="96"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="104"/>
-      <c r="N30" s="104"/>
-      <c r="O30" s="104"/>
+      <c r="K30" s="105"/>
+      <c r="L30" s="105"/>
+      <c r="M30" s="105"/>
+      <c r="N30" s="105"/>
+      <c r="O30" s="105"/>
       <c r="P30" s="97"/>
       <c r="Q30" s="97"/>
       <c r="R30" s="98"/>
@@ -3402,21 +3403,21 @@
       <c r="Z30" s="76"/>
     </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:26">
-      <c r="A31" s="107"/>
-      <c r="B31" s="108"/>
-      <c r="C31" s="109"/>
-      <c r="D31" s="109"/>
+      <c r="A31" s="108"/>
+      <c r="B31" s="109"/>
+      <c r="C31" s="110"/>
+      <c r="D31" s="110"/>
       <c r="E31" s="102"/>
-      <c r="F31" s="109"/>
-      <c r="G31" s="110"/>
-      <c r="H31" s="110"/>
-      <c r="I31" s="110"/>
-      <c r="J31" s="110"/>
-      <c r="K31" s="110"/>
-      <c r="L31" s="110"/>
-      <c r="M31" s="110"/>
-      <c r="N31" s="110"/>
-      <c r="O31" s="110"/>
+      <c r="F31" s="110"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="111"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="111"/>
+      <c r="L31" s="111"/>
+      <c r="M31" s="111"/>
+      <c r="N31" s="111"/>
+      <c r="O31" s="111"/>
       <c r="P31" s="97"/>
       <c r="Q31" s="97"/>
       <c r="R31" s="98"/>
@@ -3458,7 +3459,7 @@
       <c r="Z32" s="76"/>
     </row>
     <row r="33" ht="12.75" customHeight="1" spans="1:26">
-      <c r="A33" s="111" t="s">
+      <c r="A33" s="112" t="s">
         <v>54</v>
       </c>
       <c r="B33" s="49"/>
@@ -3466,7 +3467,7 @@
       <c r="D33" s="49"/>
       <c r="E33" s="49"/>
       <c r="F33" s="49"/>
-      <c r="G33" s="111"/>
+      <c r="G33" s="112"/>
       <c r="H33" s="1" t="s">
         <v>54</v>
       </c>
@@ -3499,7 +3500,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="111"/>
+      <c r="H34" s="112"/>
       <c r="I34" s="49"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -3520,16 +3521,16 @@
       <c r="Z34" s="1"/>
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:26">
-      <c r="A35" s="111" t="s">
+      <c r="A35" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="111"/>
+      <c r="B35" s="112"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="111" t="s">
+      <c r="H35" s="112" t="s">
         <v>57</v>
       </c>
       <c r="I35" s="1"/>
@@ -3552,16 +3553,16 @@
       <c r="Z35" s="1"/>
     </row>
     <row r="36" ht="12" customHeight="1" spans="1:26">
-      <c r="A36" s="111" t="s">
+      <c r="A36" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="B36" s="111"/>
+      <c r="B36" s="112"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="111" t="s">
+      <c r="H36" s="112" t="s">
         <v>59</v>
       </c>
       <c r="I36" s="1"/>
@@ -3584,16 +3585,16 @@
       <c r="Z36" s="1"/>
     </row>
     <row r="37" ht="12" customHeight="1" spans="1:26">
-      <c r="A37" s="111" t="s">
+      <c r="A37" s="112" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="111"/>
+      <c r="B37" s="112"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="111" t="s">
+      <c r="H37" s="112" t="s">
         <v>61</v>
       </c>
       <c r="I37" s="1"/>
@@ -3672,29 +3673,29 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" ht="28.5" customHeight="1" spans="1:26">
-      <c r="A40" s="112" t="s">
+      <c r="A40" s="113" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="113"/>
-      <c r="C40" s="113"/>
-      <c r="D40" s="113"/>
-      <c r="E40" s="114"/>
-      <c r="F40" s="114"/>
-      <c r="G40" s="114"/>
-      <c r="H40" s="112" t="s">
+      <c r="B40" s="114"/>
+      <c r="C40" s="114"/>
+      <c r="D40" s="114"/>
+      <c r="E40" s="115"/>
+      <c r="F40" s="115"/>
+      <c r="G40" s="115"/>
+      <c r="H40" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="I40" s="113"/>
-      <c r="J40" s="113"/>
-      <c r="K40" s="113"/>
-      <c r="L40" s="115"/>
-      <c r="M40" s="114"/>
-      <c r="N40" s="116"/>
-      <c r="O40" s="117"/>
-      <c r="P40" s="117"/>
-      <c r="Q40" s="117"/>
-      <c r="R40" s="118"/>
-      <c r="S40" s="118"/>
+      <c r="I40" s="114"/>
+      <c r="J40" s="114"/>
+      <c r="K40" s="114"/>
+      <c r="L40" s="116"/>
+      <c r="M40" s="115"/>
+      <c r="N40" s="117"/>
+      <c r="O40" s="118"/>
+      <c r="P40" s="118"/>
+      <c r="Q40" s="118"/>
+      <c r="R40" s="119"/>
+      <c r="S40" s="119"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
@@ -3704,31 +3705,31 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" ht="34.5" customHeight="1" spans="1:26">
-      <c r="A41" s="119" t="s">
+      <c r="A41" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="B41" s="120"/>
-      <c r="C41" s="120"/>
-      <c r="D41" s="120"/>
-      <c r="E41" s="119"/>
-      <c r="F41" s="121"/>
-      <c r="G41" s="121"/>
-      <c r="H41" s="122" t="s">
+      <c r="B41" s="121"/>
+      <c r="C41" s="121"/>
+      <c r="D41" s="121"/>
+      <c r="E41" s="120"/>
+      <c r="F41" s="122"/>
+      <c r="G41" s="122"/>
+      <c r="H41" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="I41" s="123"/>
-      <c r="J41" s="123"/>
-      <c r="K41" s="123"/>
-      <c r="L41" s="119"/>
-      <c r="M41" s="121"/>
-      <c r="N41" s="122" t="s">
+      <c r="I41" s="124"/>
+      <c r="J41" s="124"/>
+      <c r="K41" s="124"/>
+      <c r="L41" s="120"/>
+      <c r="M41" s="122"/>
+      <c r="N41" s="123" t="s">
         <v>66</v>
       </c>
-      <c r="O41" s="123"/>
-      <c r="P41" s="123"/>
-      <c r="Q41" s="123"/>
-      <c r="R41" s="124"/>
-      <c r="S41" s="124"/>
+      <c r="O41" s="124"/>
+      <c r="P41" s="124"/>
+      <c r="Q41" s="124"/>
+      <c r="R41" s="125"/>
+      <c r="S41" s="125"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
@@ -3768,27 +3769,27 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43" ht="12" customHeight="1" spans="1:26">
-      <c r="A43" s="125" t="s">
+      <c r="A43" s="126" t="s">
         <v>68</v>
       </c>
-      <c r="B43" s="126"/>
-      <c r="C43" s="126"/>
-      <c r="D43" s="126"/>
-      <c r="E43" s="126"/>
-      <c r="F43" s="126"/>
-      <c r="G43" s="126"/>
-      <c r="H43" s="126"/>
-      <c r="I43" s="126"/>
-      <c r="J43" s="126"/>
-      <c r="K43" s="126"/>
-      <c r="L43" s="126"/>
-      <c r="M43" s="126"/>
-      <c r="N43" s="126"/>
-      <c r="O43" s="126"/>
-      <c r="P43" s="126"/>
-      <c r="Q43" s="126"/>
-      <c r="R43" s="126"/>
-      <c r="S43" s="127"/>
+      <c r="B43" s="127"/>
+      <c r="C43" s="127"/>
+      <c r="D43" s="127"/>
+      <c r="E43" s="127"/>
+      <c r="F43" s="127"/>
+      <c r="G43" s="127"/>
+      <c r="H43" s="127"/>
+      <c r="I43" s="127"/>
+      <c r="J43" s="127"/>
+      <c r="K43" s="127"/>
+      <c r="L43" s="127"/>
+      <c r="M43" s="127"/>
+      <c r="N43" s="127"/>
+      <c r="O43" s="127"/>
+      <c r="P43" s="127"/>
+      <c r="Q43" s="127"/>
+      <c r="R43" s="127"/>
+      <c r="S43" s="128"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
@@ -3798,25 +3799,25 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44" ht="12" customHeight="1" spans="1:26">
-      <c r="A44" s="128"/>
-      <c r="B44" s="129"/>
-      <c r="C44" s="129"/>
-      <c r="D44" s="129"/>
-      <c r="E44" s="129"/>
-      <c r="F44" s="129"/>
-      <c r="G44" s="129"/>
-      <c r="H44" s="129"/>
-      <c r="I44" s="129"/>
-      <c r="J44" s="129"/>
-      <c r="K44" s="129"/>
-      <c r="L44" s="129"/>
-      <c r="M44" s="129"/>
-      <c r="N44" s="129"/>
-      <c r="O44" s="129"/>
-      <c r="P44" s="129"/>
-      <c r="Q44" s="129"/>
-      <c r="R44" s="129"/>
-      <c r="S44" s="130"/>
+      <c r="A44" s="129"/>
+      <c r="B44" s="130"/>
+      <c r="C44" s="130"/>
+      <c r="D44" s="130"/>
+      <c r="E44" s="130"/>
+      <c r="F44" s="130"/>
+      <c r="G44" s="130"/>
+      <c r="H44" s="130"/>
+      <c r="I44" s="130"/>
+      <c r="J44" s="130"/>
+      <c r="K44" s="130"/>
+      <c r="L44" s="130"/>
+      <c r="M44" s="130"/>
+      <c r="N44" s="130"/>
+      <c r="O44" s="130"/>
+      <c r="P44" s="130"/>
+      <c r="Q44" s="130"/>
+      <c r="R44" s="130"/>
+      <c r="S44" s="131"/>
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
@@ -3826,25 +3827,25 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45" ht="12" customHeight="1" spans="1:26">
-      <c r="A45" s="128"/>
-      <c r="B45" s="129"/>
-      <c r="C45" s="129"/>
-      <c r="D45" s="129"/>
-      <c r="E45" s="129"/>
-      <c r="F45" s="129"/>
-      <c r="G45" s="129"/>
-      <c r="H45" s="129"/>
-      <c r="I45" s="129"/>
-      <c r="J45" s="129"/>
-      <c r="K45" s="129"/>
-      <c r="L45" s="129"/>
-      <c r="M45" s="129"/>
-      <c r="N45" s="129"/>
-      <c r="O45" s="129"/>
-      <c r="P45" s="129"/>
-      <c r="Q45" s="129"/>
-      <c r="R45" s="129"/>
-      <c r="S45" s="130"/>
+      <c r="A45" s="129"/>
+      <c r="B45" s="130"/>
+      <c r="C45" s="130"/>
+      <c r="D45" s="130"/>
+      <c r="E45" s="130"/>
+      <c r="F45" s="130"/>
+      <c r="G45" s="130"/>
+      <c r="H45" s="130"/>
+      <c r="I45" s="130"/>
+      <c r="J45" s="130"/>
+      <c r="K45" s="130"/>
+      <c r="L45" s="130"/>
+      <c r="M45" s="130"/>
+      <c r="N45" s="130"/>
+      <c r="O45" s="130"/>
+      <c r="P45" s="130"/>
+      <c r="Q45" s="130"/>
+      <c r="R45" s="130"/>
+      <c r="S45" s="131"/>
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
@@ -3854,25 +3855,25 @@
       <c r="Z45" s="1"/>
     </row>
     <row r="46" ht="12.75" customHeight="1" spans="1:26">
-      <c r="A46" s="131"/>
-      <c r="B46" s="132"/>
-      <c r="C46" s="132"/>
-      <c r="D46" s="132"/>
-      <c r="E46" s="132"/>
-      <c r="F46" s="132"/>
-      <c r="G46" s="132"/>
-      <c r="H46" s="132"/>
-      <c r="I46" s="132"/>
-      <c r="J46" s="132"/>
-      <c r="K46" s="132"/>
-      <c r="L46" s="132"/>
-      <c r="M46" s="132"/>
-      <c r="N46" s="132"/>
-      <c r="O46" s="132"/>
-      <c r="P46" s="132"/>
-      <c r="Q46" s="132"/>
-      <c r="R46" s="132"/>
-      <c r="S46" s="133"/>
+      <c r="A46" s="132"/>
+      <c r="B46" s="133"/>
+      <c r="C46" s="133"/>
+      <c r="D46" s="133"/>
+      <c r="E46" s="133"/>
+      <c r="F46" s="133"/>
+      <c r="G46" s="133"/>
+      <c r="H46" s="133"/>
+      <c r="I46" s="133"/>
+      <c r="J46" s="133"/>
+      <c r="K46" s="133"/>
+      <c r="L46" s="133"/>
+      <c r="M46" s="133"/>
+      <c r="N46" s="133"/>
+      <c r="O46" s="133"/>
+      <c r="P46" s="133"/>
+      <c r="Q46" s="133"/>
+      <c r="R46" s="133"/>
+      <c r="S46" s="134"/>
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
@@ -4134,7 +4135,7 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" ht="9.75" customHeight="1" spans="1:26">
-      <c r="A56" s="134"/>
+      <c r="A56" s="135"/>
       <c r="O56" s="1"/>
       <c r="P56" s="1"/>
       <c r="Q56" s="1"/>

--- a/resources/templates/Report on Appointment Issued.xlsx
+++ b/resources/templates/Report on Appointment Issued.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="87">
   <si>
     <t>CS Form No. 2</t>
   </si>
@@ -191,13 +191,16 @@
     <t>${employment_status}</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>${substitute_from} to ${substitute_to}</t>
   </si>
   <si>
     <t>${appointment_nature}</t>
   </si>
   <si>
-    <t>06/02/2026 TO O6/15/2026</t>
+    <t>${publication_date_from} to ${publication_date_to}</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>CERTIFICATION:</t>
@@ -2163,10 +2166,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3194,7 +3193,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" ht="45" spans="1:26">
+    <row r="25" ht="60" spans="1:26">
       <c r="A25" s="90">
         <v>1</v>
       </c>
@@ -3234,11 +3233,11 @@
       <c r="M25" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="N25" s="136" t="s">
+      <c r="N25" s="93" t="s">
         <v>53</v>
       </c>
       <c r="O25" s="93" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P25" s="97"/>
       <c r="Q25" s="97"/>
@@ -3460,7 +3459,7 @@
     </row>
     <row r="33" ht="12.75" customHeight="1" spans="1:26">
       <c r="A33" s="112" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33" s="49"/>
       <c r="C33" s="49"/>
@@ -3469,7 +3468,7 @@
       <c r="F33" s="49"/>
       <c r="G33" s="112"/>
       <c r="H33" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -3477,7 +3476,7 @@
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
@@ -3522,7 +3521,7 @@
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:26">
       <c r="A35" s="112" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35" s="112"/>
       <c r="C35" s="1"/>
@@ -3531,7 +3530,7 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="112" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -3554,7 +3553,7 @@
     </row>
     <row r="36" ht="12" customHeight="1" spans="1:26">
       <c r="A36" s="112" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B36" s="112"/>
       <c r="C36" s="1"/>
@@ -3563,7 +3562,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="112" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -3586,7 +3585,7 @@
     </row>
     <row r="37" ht="12" customHeight="1" spans="1:26">
       <c r="A37" s="112" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B37" s="112"/>
       <c r="C37" s="1"/>
@@ -3595,7 +3594,7 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="112" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -3674,7 +3673,7 @@
     </row>
     <row r="40" ht="28.5" customHeight="1" spans="1:26">
       <c r="A40" s="113" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B40" s="114"/>
       <c r="C40" s="114"/>
@@ -3683,7 +3682,7 @@
       <c r="F40" s="115"/>
       <c r="G40" s="115"/>
       <c r="H40" s="113" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I40" s="114"/>
       <c r="J40" s="114"/>
@@ -3706,7 +3705,7 @@
     </row>
     <row r="41" ht="34.5" customHeight="1" spans="1:26">
       <c r="A41" s="120" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B41" s="121"/>
       <c r="C41" s="121"/>
@@ -3715,7 +3714,7 @@
       <c r="F41" s="122"/>
       <c r="G41" s="122"/>
       <c r="H41" s="123" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I41" s="124"/>
       <c r="J41" s="124"/>
@@ -3723,7 +3722,7 @@
       <c r="L41" s="120"/>
       <c r="M41" s="122"/>
       <c r="N41" s="123" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O41" s="124"/>
       <c r="P41" s="124"/>
@@ -3740,7 +3739,7 @@
     </row>
     <row r="42" ht="13.5" customHeight="1" spans="1:26">
       <c r="A42" s="52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B42" s="52"/>
       <c r="C42" s="25"/>
@@ -3770,7 +3769,7 @@
     </row>
     <row r="43" ht="12" customHeight="1" spans="1:26">
       <c r="A43" s="126" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B43" s="127"/>
       <c r="C43" s="127"/>
@@ -30538,14 +30537,14 @@
     </row>
     <row r="2" ht="20.25" customHeight="1" spans="1:26">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -30572,7 +30571,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:26">
       <c r="A3" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -30605,13 +30604,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -30641,13 +30640,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -30677,13 +30676,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -30713,13 +30712,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -30749,13 +30748,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -30785,13 +30784,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -30821,13 +30820,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -30856,10 +30855,10 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -30888,10 +30887,10 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -30921,7 +30920,7 @@
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>

--- a/resources/templates/Report on Appointment Issued.xlsx
+++ b/resources/templates/Report on Appointment Issued.xlsx
@@ -46,7 +46,7 @@
     <t>REPORT ON APPOINTMENTS ISSUED (RAI)</t>
   </si>
   <si>
-    <t>For the month of June 2026</t>
+    <t>For the month of ${current_date}</t>
   </si>
   <si>
     <t>For CSC RO/FO's Use:</t>
